--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N5_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N5_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>13.22408830307263</v>
+        <v>2.148914349249303</v>
       </c>
       <c r="D2" t="n">
-        <v>12.19153719687796</v>
+        <v>1.981124794492668</v>
       </c>
       <c r="E2" t="n">
-        <v>34.10519927521654</v>
+        <v>5.542094882222689</v>
       </c>
       <c r="F2" t="n">
-        <v>33.87097922938559</v>
+        <v>5.50403412477516</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>60.50669813462465</v>
+        <v>9.832338446876506</v>
       </c>
       <c r="D3" t="n">
-        <v>59.08604359693707</v>
+        <v>9.601482084502274</v>
       </c>
       <c r="E3" t="n">
-        <v>34.10519927521654</v>
+        <v>5.542094882222689</v>
       </c>
       <c r="F3" t="n">
-        <v>33.87097922938559</v>
+        <v>5.50403412477516</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>107.5623352621425</v>
+        <v>17.47887948009816</v>
       </c>
       <c r="D4" t="n">
-        <v>105.7852158209474</v>
+        <v>17.19009757090395</v>
       </c>
       <c r="E4" t="n">
-        <v>34.10519927521654</v>
+        <v>5.542094882222689</v>
       </c>
       <c r="F4" t="n">
-        <v>33.87097922938559</v>
+        <v>5.50403412477516</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.46141606164634</v>
+        <v>4.949980110017531</v>
       </c>
       <c r="D5" t="n">
-        <v>30.24180183418146</v>
+        <v>4.914292798054487</v>
       </c>
       <c r="E5" t="n">
-        <v>34.10519927521654</v>
+        <v>5.542094882222689</v>
       </c>
       <c r="F5" t="n">
-        <v>33.87097922938559</v>
+        <v>5.50403412477516</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>82.35649227213744</v>
+        <v>13.38292999422234</v>
       </c>
       <c r="D6" t="n">
-        <v>82.13998128777838</v>
+        <v>13.34774695926399</v>
       </c>
       <c r="E6" t="n">
-        <v>34.10519927521654</v>
+        <v>5.542094882222689</v>
       </c>
       <c r="F6" t="n">
-        <v>33.87097922938559</v>
+        <v>5.50403412477516</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
